--- a/Result/profitability/1463.xlsx
+++ b/Result/profitability/1463.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>0.41125</v>
+        <v>0.36875</v>
       </c>
       <c r="N2" t="n">
-        <v>-11.01875</v>
+        <v>-11.4425</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.365</v>
+        <v>-0.0275</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.15</v>
+        <v>-14.78125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>-0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0225</v>
+        <v>-0.09999999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.59</v>
+        <v>-18.25125</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.9</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1975</v>
+        <v>-0.17875</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.515</v>
+        <v>-17.025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1675</v>
+        <v>-0.2525</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.24375</v>
+        <v>-14.6975</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.22375</v>
+        <v>-0.15875</v>
       </c>
       <c r="N7" t="n">
-        <v>-12.84</v>
+        <v>5.497499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.12625</v>
+        <v>-0.14</v>
       </c>
       <c r="N8" t="n">
-        <v>8.712499999999999</v>
+        <v>6.373749999999998</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.73</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.03374999999999999</v>
+        <v>-0.03375</v>
       </c>
       <c r="N9" t="n">
         <v>11.42</v>
@@ -1645,7 +1645,7 @@
         <v>-0.11</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.03624999999999999</v>
+        <v>-0.03625</v>
       </c>
       <c r="N10" t="n">
         <v>10.94625</v>
@@ -1772,7 +1772,7 @@
         <v>0.16</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002500000000000009</v>
+        <v>0.002499999999999995</v>
       </c>
       <c r="N11" t="n">
         <v>13.81375</v>
@@ -1899,7 +1899,7 @@
         <v>0.03</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01625000000000001</v>
+        <v>0.01624999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>15.36375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>52</v>
+      </c>
+      <c r="D75" t="n">
+        <v>53</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-38.28%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-11.96875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-18.71</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.096717467760844</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5555555555555556</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.8784082535003684</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
